--- a/data/trans_camb/IP19C09-Edad-trans_camb.xlsx
+++ b/data/trans_camb/IP19C09-Edad-trans_camb.xlsx
@@ -631,7 +631,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 76,67</t>
+          <t>0,0; 79,51</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -651,7 +651,7 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 65,4</t>
+          <t>0,0; 66,46</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -787,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,7; 6,94</t>
+          <t>-1,52; 6,19</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,49; 10,1</t>
+          <t>-1,33; 9,68</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-7,45; 2,46</t>
+          <t>-8,12; 2,54</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-5,8; 5,94</t>
+          <t>-6,62; 5,73</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-3,63; 2,9</t>
+          <t>-3,82; 2,84</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-2,52; 5,49</t>
+          <t>-2,15; 5,42</t>
         </is>
       </c>
     </row>
@@ -873,22 +873,22 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-88,78; 111,59</t>
+          <t>-89,37; 160,03</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-75,42; 203,23</t>
+          <t>-76,65; 243,54</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-74,63; 145,01</t>
+          <t>-74,11; 156,1</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-60,67; 262,84</t>
+          <t>-49,53; 267,44</t>
         </is>
       </c>
     </row>
@@ -943,32 +943,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-4,72; 0,55</t>
+          <t>-4,22; 0,97</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,99; 4,67</t>
+          <t>-1,61; 4,72</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-0,73; 4,2</t>
+          <t>-0,73; 4,79</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-1,24; 2,15</t>
+          <t>-1,4; 1,98</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-1,64; 2,0</t>
+          <t>-1,67; 1,82</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-0,82; 2,73</t>
+          <t>-0,89; 2,61</t>
         </is>
       </c>
     </row>
@@ -1024,7 +1024,7 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-86,89; —</t>
+          <t>-71,52; —</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -1039,12 +1039,12 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-56,23; 832,95</t>
+          <t>-65,66; 692,97</t>
         </is>
       </c>
     </row>
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1,79; 2,97</t>
+          <t>-1,75; 2,64</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-2,18; 1,83</t>
+          <t>-2,08; 1,89</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-5,33; -0,08</t>
+          <t>-5,1; -0,24</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-4,37; 1,71</t>
+          <t>-4,33; 1,97</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-3,07; 0,59</t>
+          <t>-2,92; 0,48</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-2,63; 1,28</t>
+          <t>-2,67; 1,2</t>
         </is>
       </c>
     </row>
@@ -1185,22 +1185,22 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 59,22</t>
+          <t>-100,0; 60,54</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-87,94; 107,51</t>
+          <t>-86,02; 107,29</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-88,79; 60,41</t>
+          <t>-88,26; 55,43</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-78,14; 99,54</t>
+          <t>-80,34; 93,66</t>
         </is>
       </c>
     </row>
@@ -1255,32 +1255,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-1,17; 1,79</t>
+          <t>-1,37; 1,94</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-0,49; 3,06</t>
+          <t>-0,7; 3,03</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-3,14; 0,79</t>
+          <t>-3,02; 0,47</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-2,63; 1,56</t>
+          <t>-2,65; 1,38</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-1,69; 0,73</t>
+          <t>-1,74; 0,72</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-1,08; 1,51</t>
+          <t>-1,03; 1,64</t>
         </is>
       </c>
     </row>
@@ -1331,32 +1331,32 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-62,92; 313,53</t>
+          <t>-65,09; 269,82</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-37,11; 454,94</t>
+          <t>-38,55; 417,3</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-76,29; 40,49</t>
+          <t>-78,16; 31,07</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-66,26; 83,44</t>
+          <t>-64,12; 72,04</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-60,39; 48,28</t>
+          <t>-60,11; 54,03</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-37,48; 94,41</t>
+          <t>-37,04; 103,19</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP19C09-Edad-trans_camb.xlsx
+++ b/data/trans_camb/IP19C09-Edad-trans_camb.xlsx
@@ -631,7 +631,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 79,51</t>
+          <t>0,0; 78,85</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -651,7 +651,7 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 66,46</t>
+          <t>0,0; 65,65</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -787,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,52; 6,19</t>
+          <t>-2,02; 6,44</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,33; 9,68</t>
+          <t>-1,1; 9,62</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-8,12; 2,54</t>
+          <t>-7,75; 2,84</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-6,62; 5,73</t>
+          <t>-5,69; 6,74</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-3,82; 2,84</t>
+          <t>-3,42; 3,12</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-2,15; 5,42</t>
+          <t>-2,21; 5,64</t>
         </is>
       </c>
     </row>
@@ -873,22 +873,22 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-89,37; 160,03</t>
+          <t>-88,19; 147,86</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-76,65; 243,54</t>
+          <t>-71,09; 266,45</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-74,11; 156,1</t>
+          <t>-70,06; 186,91</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-49,53; 267,44</t>
+          <t>-50,82; 300,32</t>
         </is>
       </c>
     </row>
@@ -943,32 +943,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-4,22; 0,97</t>
+          <t>-4,72; 0,54</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,61; 4,72</t>
+          <t>-1,98; 4,42</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-0,73; 4,79</t>
+          <t>-0,75; 4,18</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-1,4; 1,98</t>
+          <t>-1,51; 2,19</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-1,67; 1,82</t>
+          <t>-1,64; 1,72</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-0,89; 2,61</t>
+          <t>-0,9; 2,73</t>
         </is>
       </c>
     </row>
@@ -1024,7 +1024,7 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-71,52; —</t>
+          <t>-72,03; —</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -1044,7 +1044,7 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-65,66; 692,97</t>
+          <t>-62,81; 919,2</t>
         </is>
       </c>
     </row>
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1,75; 2,64</t>
+          <t>-1,88; 2,81</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-2,08; 1,89</t>
+          <t>-2,08; 1,84</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-5,1; -0,24</t>
+          <t>-5,04; -0,12</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-4,33; 1,97</t>
+          <t>-3,91; 1,81</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-2,92; 0,48</t>
+          <t>-2,9; 0,53</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-2,67; 1,2</t>
+          <t>-2,72; 0,98</t>
         </is>
       </c>
     </row>
@@ -1185,22 +1185,22 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 60,54</t>
+          <t>-100,0; 27,31</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-86,02; 107,29</t>
+          <t>-85,95; 123,63</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-88,26; 55,43</t>
+          <t>-85,86; 67,42</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-80,34; 93,66</t>
+          <t>-82,94; 70,21</t>
         </is>
       </c>
     </row>
@@ -1255,32 +1255,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-1,37; 1,94</t>
+          <t>-1,17; 1,85</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-0,7; 3,03</t>
+          <t>-0,45; 2,9</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-3,02; 0,47</t>
+          <t>-3,15; 0,66</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-2,65; 1,38</t>
+          <t>-2,65; 1,35</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-1,74; 0,72</t>
+          <t>-1,78; 0,73</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-1,03; 1,64</t>
+          <t>-1,0; 1,5</t>
         </is>
       </c>
     </row>
@@ -1331,32 +1331,32 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-65,09; 269,82</t>
+          <t>-60,85; 267,64</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-38,55; 417,3</t>
+          <t>-35,38; 408,48</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-78,16; 31,07</t>
+          <t>-75,74; 42,4</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-64,12; 72,04</t>
+          <t>-65,43; 69,45</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-60,11; 54,03</t>
+          <t>-60,94; 48,64</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-37,04; 103,19</t>
+          <t>-36,1; 92,91</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP19C09-Edad-trans_camb.xlsx
+++ b/data/trans_camb/IP19C09-Edad-trans_camb.xlsx
@@ -519,13 +519,13 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="F1" s="3" t="n"/>
@@ -593,17 +593,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
           <t>18,84</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -631,7 +631,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 78,85</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -641,7 +641,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 76,67</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -651,7 +651,7 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 65,65</t>
+          <t>0,0; 65,4</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -669,17 +669,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
           <t>inf%</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -749,22 +749,22 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>-2,38</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>-0,13</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
           <t>1,53</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>2,77</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>-2,38</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>-0,13</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -787,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-2,02; 6,44</t>
+          <t>-7,45; 2,46</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,1; 9,62</t>
+          <t>-5,8; 5,94</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-7,75; 2,84</t>
+          <t>-1,7; 6,94</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-5,69; 6,74</t>
+          <t>-1,49; 10,1</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-3,42; 3,12</t>
+          <t>-3,63; 2,9</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-2,21; 5,64</t>
+          <t>-2,52; 5,49</t>
         </is>
       </c>
     </row>
@@ -825,22 +825,22 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>-42,72%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>-2,27%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
           <t>103,31%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
         <is>
           <t>186,95%</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>-42,72%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>-2,27%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -863,32 +863,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-88,78; 111,59</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-75,42; 203,23</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-88,19; 147,86</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-71,09; 266,45</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-70,06; 186,91</t>
+          <t>-74,63; 145,01</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-50,82; 300,32</t>
+          <t>-60,67; 262,84</t>
         </is>
       </c>
     </row>
@@ -905,22 +905,22 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>1,18</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>0,34</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
           <t>-1,02</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="F12" s="2" t="inlineStr">
         <is>
           <t>1,65</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>1,18</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>0,34</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -943,32 +943,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-4,72; 0,54</t>
+          <t>-0,73; 4,2</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,98; 4,42</t>
+          <t>-1,24; 2,15</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-0,75; 4,18</t>
+          <t>-4,72; 0,55</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-1,51; 2,19</t>
+          <t>-1,99; 4,67</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-1,64; 1,72</t>
+          <t>-1,64; 2,0</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-0,9; 2,73</t>
+          <t>-0,82; 2,73</t>
         </is>
       </c>
     </row>
@@ -981,22 +981,22 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>191,64%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>54,76%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
           <t>-65,48%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="F14" s="2" t="inlineStr">
         <is>
           <t>105,75%</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>191,64%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>54,76%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1024,7 +1024,7 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-72,03; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -1034,17 +1034,17 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-86,89; —</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; —</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-62,81; 919,2</t>
+          <t>-56,23; 832,95</t>
         </is>
       </c>
     </row>
@@ -1061,22 +1061,22 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>-2,45</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>-1,23</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
           <t>0,17</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="F16" s="2" t="inlineStr">
         <is>
           <t>-0,21</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>-2,45</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>-1,23</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1,88; 2,81</t>
+          <t>-5,33; -0,08</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-2,08; 1,84</t>
+          <t>-4,37; 1,71</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-5,04; -0,12</t>
+          <t>-1,79; 2,97</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-3,91; 1,81</t>
+          <t>-2,18; 1,83</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-2,9; 0,53</t>
+          <t>-3,07; 0,59</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-2,72; 0,98</t>
+          <t>-2,63; 1,28</t>
         </is>
       </c>
     </row>
@@ -1137,22 +1137,22 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>-71,34%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>-35,81%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
           <t>12,91%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="F18" s="2" t="inlineStr">
         <is>
           <t>-16,53%</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>-71,34%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>-35,81%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1175,32 +1175,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 59,22</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-87,94; 107,51</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 27,31</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-85,95; 123,63</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-85,86; 67,42</t>
+          <t>-88,79; 60,41</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-82,94; 70,21</t>
+          <t>-78,14; 99,54</t>
         </is>
       </c>
     </row>
@@ -1217,22 +1217,22 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>-1,24</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>-0,65</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
           <t>0,24</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="F20" s="2" t="inlineStr">
         <is>
           <t>1,15</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>-1,24</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>-0,65</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1255,32 +1255,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-1,17; 1,85</t>
+          <t>-3,14; 0,79</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-0,45; 2,9</t>
+          <t>-2,63; 1,56</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-3,15; 0,66</t>
+          <t>-1,17; 1,79</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-2,65; 1,35</t>
+          <t>-0,49; 3,06</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-1,78; 0,73</t>
+          <t>-1,69; 0,73</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-1,0; 1,5</t>
+          <t>-1,08; 1,51</t>
         </is>
       </c>
     </row>
@@ -1293,22 +1293,22 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>-40,5%</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>-21,11%</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
           <t>16,93%</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="F22" s="2" t="inlineStr">
         <is>
           <t>82,66%</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>-40,5%</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>-21,11%</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -1331,32 +1331,32 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-60,85; 267,64</t>
+          <t>-76,29; 40,49</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-35,38; 408,48</t>
+          <t>-66,26; 83,44</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-75,74; 42,4</t>
+          <t>-62,92; 313,53</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-65,43; 69,45</t>
+          <t>-37,11; 454,94</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-60,94; 48,64</t>
+          <t>-60,39; 48,28</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-36,1; 92,91</t>
+          <t>-37,48; 94,41</t>
         </is>
       </c>
     </row>
